--- a/Content/Examples/test.xlsx
+++ b/Content/Examples/test.xlsx
@@ -544,7 +544,7 @@
     <t>25-34 years</t>
   </si>
   <si>
-    <t>GMTA</t>
+    <t>GMAT</t>
   </si>
   <si>
     <t>80-84</t>
